--- a/backend-infra-ti/src/main/resources/data/inventario.xlsx
+++ b/backend-infra-ti/src/main/resources/data/inventario.xlsx
@@ -20,6 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventiladores" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ControladoraRaid" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PuertoSwitch" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChasisBlade" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChasisSlot" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2001,6 +2003,164 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cantidad_slots</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>chasisID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>numeroSlot</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>hostanameServidor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Ocupado</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>srv-blade01</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Libre</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/backend-infra-ti/src/main/resources/data/inventario.xlsx
+++ b/backend-infra-ti/src/main/resources/data/inventario.xlsx
@@ -2,21 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActivosTI" sheetId="1" r:id="R6d8e54a9b60a48bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="2" r:id="Re61949a53091412a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage" sheetId="3" r:id="Rceae782a59114214"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switches" sheetId="4" r:id="Rae6340d5bb0b4c88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cpu" sheetId="5" r:id="R84e4c35099934d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ram" sheetId="6" r:id="Rf23420f7b5474474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discos" sheetId="7" r:id="R14d070faf7d04f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TarjetasRed" sheetId="8" r:id="R33762462b6da420d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PuertoTarjetaRed" sheetId="9" r:id="R99dd3c05d7e34ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FuentesPoder" sheetId="10" r:id="R829fbb5bd7ba4a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventiladores" sheetId="11" r:id="Rf492321aaeac4826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ControladoraRaid" sheetId="12" r:id="Ra21e70aebb514fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PuertoSwitch" sheetId="13" r:id="R06106240b8414988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChasisBlade" sheetId="14" r:id="Ref55d32bd4954030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChasisSlot" sheetId="15" r:id="Rb2812dd18e504fda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ActivosTI" sheetId="1" r:id="R3543577f19284d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servidores" sheetId="2" r:id="R3fbdceff752e41d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Storage" sheetId="3" r:id="Red3b660dc8ec4f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switches" sheetId="4" r:id="R29970f6a74e54b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cpu" sheetId="5" r:id="R66d8cba21cfa48e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ram" sheetId="6" r:id="Re46fc664b60c4ea6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Discos" sheetId="7" r:id="R3b8778465a474c52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TarjetasRed" sheetId="8" r:id="R10fc114866594a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PuertoTarjetaRed" sheetId="9" r:id="R9ea6d801121d4bb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FuentesPoder" sheetId="10" r:id="R2c01fb040e3d4306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ventiladores" sheetId="11" r:id="R3286f0ba3b3b458b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ControladoraRaid" sheetId="12" r:id="R2a3d70555695400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PuertoSwitch" sheetId="13" r:id="Rddc71eda00b549be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChasisBlade" sheetId="14" r:id="R2de5d1a582aa4fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChasisSlot" sheetId="15" r:id="R2cf2ed4b6f3f45a8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -353,7 +353,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -380,6 +380,12 @@
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color theme="1"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
   <x:fills count="2">
     <x:fill>
@@ -395,7 +401,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0"/>
@@ -407,6 +413,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1987,7 +1994,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R565c70ede62f4221"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c0a3cbdf26d4690"/>
 </x:worksheet>
 </file>
 
@@ -2808,7 +2815,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99b48584188b4291"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0347cc56e8b54977"/>
 </x:worksheet>
 </file>
 
@@ -3541,7 +3548,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7923da1c17604d2f"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc664b91d6f104e0d"/>
 </x:worksheet>
 </file>
 
@@ -5896,7 +5903,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra19ed52c288a4280"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f08de93533b4a4d"/>
 </x:worksheet>
 </file>
 
@@ -6617,7 +6624,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reab4b39240064f1a"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fc44d25ab584392"/>
 </x:worksheet>
 </file>
 
@@ -7487,7 +7494,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d4bc724fa134b92"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3a15451cf4743a3"/>
 </x:worksheet>
 </file>
 
@@ -8832,7 +8839,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd238e3c97e4a42d0"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc80e41b602fb490b"/>
 </x:worksheet>
 </file>
 
@@ -8848,6 +8855,7 @@
     <x:col min="6" max="6" width="14" customWidth="1"/>
     <x:col min="7" max="7" width="15" customWidth="1"/>
     <x:col min="8" max="8" width="11" customWidth="1"/>
+    <x:col min="9" max="9" width="50" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -8891,6 +8899,9 @@
           <x:t xml:space="preserve">estado</x:t>
         </x:is>
       </x:c>
+      <x:c r="I1" s="11" t="str">
+        <x:v>modelo</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="7" t="n">
@@ -8925,6 +8936,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I2" s="8" t="str">
+        <x:v>HPE 1.2TB SAS 12G Enterprise 10K SFF SC HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="7" t="n">
@@ -8959,6 +8973,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I3" s="8" t="str">
+        <x:v>HPE 1.2TB SAS 12G Enterprise 10K SFF SC HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="7" t="n">
@@ -8993,6 +9010,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I4" s="8" t="str">
+        <x:v>Dell 3.84TB Enterprise NVMe Read Intensive U.2 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="7" t="n">
@@ -9027,6 +9047,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I5" s="8" t="str">
+        <x:v>HPE MSA 2060 64GB System Flash Module</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="7" t="n">
@@ -9057,6 +9080,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I6" s="8" t="str">
+        <x:v>HPE 3.84TB SAS 12G Read Intensive SFF SC SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="7" t="n">
@@ -9087,6 +9113,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I7" s="8" t="str">
+        <x:v>HPE 3.84TB SAS 12G Read Intensive SFF SC SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="7" t="n">
@@ -9121,6 +9150,9 @@
           <x:t xml:space="preserve">Encendido</x:t>
         </x:is>
       </x:c>
+      <x:c r="I8" s="8" t="str">
+        <x:v>Dell 1.2TB 10K SAS 12Gbps 2.5in Hot-Plug HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="7" t="n">
@@ -9155,6 +9187,9 @@
           <x:t xml:space="preserve">Degradado</x:t>
         </x:is>
       </x:c>
+      <x:c r="I9" s="8" t="str">
+        <x:v>Dell 1.2TB 10K SAS 12Gbps 2.5in Hot-Plug HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="8" t="n">
@@ -9181,6 +9216,9 @@
       <x:c r="H10" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I10" s="8" t="str">
+        <x:v>HPE 960GB SAS 12G Read Intensive SFF SC SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="8" t="n">
@@ -9207,6 +9245,9 @@
       <x:c r="H11" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I11" s="8" t="str">
+        <x:v>HPE 960GB SAS 12G Read Intensive SFF SC SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="8" t="n">
@@ -9233,6 +9274,9 @@
       <x:c r="H12" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I12" s="8" t="str">
+        <x:v>HPE 1.92TB NVMe Gen4 Mixed Use SFF U.3 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="8" t="n">
@@ -9259,6 +9303,9 @@
       <x:c r="H13" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I13" s="8" t="str">
+        <x:v>HPE 1.92TB NVMe Gen4 Mixed Use SFF U.3 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="8" t="n">
@@ -9285,6 +9332,9 @@
       <x:c r="H14" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I14" s="8" t="str">
+        <x:v>Huawei 1.2TB 10K SAS 12Gbps 2.5in HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="8" t="n">
@@ -9311,6 +9361,9 @@
       <x:c r="H15" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I15" s="8" t="str">
+        <x:v>Huawei 1.2TB 10K SAS 12Gbps 2.5in HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="8" t="n">
@@ -9337,6 +9390,9 @@
       <x:c r="H16" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I16" s="8" t="str">
+        <x:v>Huawei 480GB SATA 6Gbps Read Intensive 2.5in SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="8" t="n">
@@ -9363,6 +9419,9 @@
       <x:c r="H17" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I17" s="8" t="str">
+        <x:v>Huawei 480GB SATA 6Gbps Read Intensive 2.5in SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="8" t="n">
@@ -9389,6 +9448,9 @@
       <x:c r="H18" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I18" s="8" t="str">
+        <x:v>HPE 1.92TB NVMe Gen4 Mixed Use SFF U.3 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="8" t="n">
@@ -9415,6 +9477,9 @@
       <x:c r="H19" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I19" s="8" t="str">
+        <x:v>HPE 1.92TB NVMe Gen4 Mixed Use SFF U.3 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="8" t="n">
@@ -9441,6 +9506,9 @@
       <x:c r="H20" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I20" s="8" t="str">
+        <x:v>HPE 3.84TB NVMe Gen4 Read Intensive SFF U.3 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="8" t="n">
@@ -9467,6 +9535,9 @@
       <x:c r="H21" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I21" s="8" t="str">
+        <x:v>HPE 3.84TB NVMe Gen4 Read Intensive SFF U.3 SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="8" t="n">
@@ -9493,6 +9564,9 @@
       <x:c r="H22" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I22" s="8" t="str">
+        <x:v>Huawei 1.2TB 10K SAS 12Gbps 2.5in HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="8" t="n">
@@ -9519,6 +9593,9 @@
       <x:c r="H23" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I23" s="8" t="str">
+        <x:v>Huawei 1.2TB 10K SAS 12Gbps 2.5in HDD</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="8" t="n">
@@ -9545,6 +9622,9 @@
       <x:c r="H24" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I24" s="8" t="str">
+        <x:v>HPE Alletra 6000 3.84TB NVMe SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="8" t="n">
@@ -9571,6 +9651,9 @@
       <x:c r="H25" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I25" s="8" t="str">
+        <x:v>HPE Alletra 6000 3.84TB NVMe SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="8" t="n">
@@ -9597,6 +9680,9 @@
       <x:c r="H26" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I26" s="8" t="str">
+        <x:v>Huawei OceanStor Dorado 7.68TB NVMe SSD</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="8" t="n">
@@ -9623,10 +9709,13 @@
       <x:c r="H27" s="8" t="str">
         <x:v>Encendido</x:v>
       </x:c>
+      <x:c r="I27" s="8" t="str">
+        <x:v>Huawei OceanStor Dorado 7.68TB NVMe SSD</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2f78ffcf9d347df"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ac5a05928964180"/>
 </x:worksheet>
 </file>
 
@@ -10100,7 +10189,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6422138428748d1"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce812b55c8aa4e84"/>
 </x:worksheet>
 </file>
 
